--- a/AAII_Financials/Quarterly/MBKL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBKL_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/MBKL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBKL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>MBKL</t>
   </si>
@@ -720,11 +720,11 @@
       <c r="E8" s="3">
         <v>3700</v>
       </c>
-      <c r="F8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3700</v>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <v>3900</v>
@@ -732,8 +732,8 @@
       <c r="I8" s="3">
         <v>3900</v>
       </c>
-      <c r="J8" s="3">
-        <v>4100</v>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>4100</v>
@@ -778,11 +778,11 @@
       <c r="E10" s="3">
         <v>3700</v>
       </c>
-      <c r="F10" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3700</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="3">
         <v>3900</v>
@@ -790,8 +790,8 @@
       <c r="I10" s="3">
         <v>3900</v>
       </c>
-      <c r="J10" s="3">
-        <v>4100</v>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3">
         <v>4100</v>
@@ -908,10 +908,10 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -920,7 +920,7 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
@@ -946,11 +946,11 @@
       <c r="E17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2900</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="3">
         <v>3000</v>
@@ -958,8 +958,8 @@
       <c r="I17" s="3">
         <v>3000</v>
       </c>
-      <c r="J17" s="3">
-        <v>3200</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3">
         <v>3200</v>
@@ -975,11 +975,11 @@
       <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
-        <v>800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>800</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H18" s="3">
         <v>800</v>
@@ -987,8 +987,8 @@
       <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
-        <v>900</v>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3">
         <v>900</v>
@@ -1047,10 +1047,10 @@
         <v>1000</v>
       </c>
       <c r="F21" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>1000</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="J21" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>1100</v>
@@ -1104,11 +1104,11 @@
       <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
-        <v>800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>800</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="3">
         <v>800</v>
@@ -1116,8 +1116,8 @@
       <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
-        <v>900</v>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3">
         <v>900</v>
@@ -1133,11 +1133,11 @@
       <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
@@ -1145,8 +1145,8 @@
       <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>300</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
@@ -1191,11 +1191,11 @@
       <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
-        <v>500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>500</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H26" s="3">
         <v>600</v>
@@ -1203,8 +1203,8 @@
       <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
-        <v>600</v>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3">
         <v>600</v>
@@ -1220,11 +1220,11 @@
       <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
-        <v>500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>500</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="3">
         <v>600</v>
@@ -1232,8 +1232,8 @@
       <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="J27" s="3">
-        <v>600</v>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3">
         <v>600</v>
@@ -1394,11 +1394,11 @@
       <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
-        <v>500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>500</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H33" s="3">
         <v>600</v>
@@ -1406,8 +1406,8 @@
       <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
-        <v>600</v>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3">
         <v>600</v>
@@ -1452,11 +1452,11 @@
       <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
-        <v>500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>500</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H35" s="3">
         <v>600</v>
@@ -1464,8 +1464,8 @@
       <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
-        <v>600</v>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3">
         <v>600</v>
@@ -1541,11 +1541,11 @@
       <c r="E41" s="3">
         <v>9000</v>
       </c>
-      <c r="F41" s="3">
-        <v>37200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>37200</v>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="3">
         <v>33700</v>
@@ -1553,8 +1553,8 @@
       <c r="I41" s="3">
         <v>33700</v>
       </c>
-      <c r="J41" s="3">
-        <v>29200</v>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K41" s="3">
         <v>29200</v>
@@ -1686,11 +1686,11 @@
       <c r="E46" s="3">
         <v>36000</v>
       </c>
-      <c r="F46" s="3">
-        <v>37200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>37200</v>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H46" s="3">
         <v>35200</v>
@@ -1698,8 +1698,8 @@
       <c r="I46" s="3">
         <v>35200</v>
       </c>
-      <c r="J46" s="3">
-        <v>29200</v>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K46" s="3">
         <v>29200</v>
@@ -1715,11 +1715,11 @@
       <c r="E47" s="3">
         <v>80600</v>
       </c>
-      <c r="F47" s="3">
-        <v>70800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>70800</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3">
         <v>71700</v>
@@ -1727,8 +1727,8 @@
       <c r="I47" s="3">
         <v>71700</v>
       </c>
-      <c r="J47" s="3">
-        <v>65200</v>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>65200</v>
@@ -1744,11 +1744,11 @@
       <c r="E48" s="3">
         <v>11600</v>
       </c>
-      <c r="F48" s="3">
-        <v>11700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>11700</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
         <v>11800</v>
@@ -1756,8 +1756,8 @@
       <c r="I48" s="3">
         <v>11800</v>
       </c>
-      <c r="J48" s="3">
-        <v>12000</v>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>12000</v>
@@ -1773,11 +1773,11 @@
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -1785,8 +1785,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -1860,11 +1860,11 @@
       <c r="E52" s="3">
         <v>3800</v>
       </c>
-      <c r="F52" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>7200</v>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H52" s="3">
         <v>4300</v>
@@ -1872,8 +1872,8 @@
       <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="J52" s="3">
-        <v>6900</v>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>6900</v>
@@ -1918,11 +1918,11 @@
       <c r="E54" s="3">
         <v>339100</v>
       </c>
-      <c r="F54" s="3">
-        <v>339600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>339600</v>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H54" s="3">
         <v>331000</v>
@@ -1930,8 +1930,8 @@
       <c r="I54" s="3">
         <v>331000</v>
       </c>
-      <c r="J54" s="3">
-        <v>325100</v>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K54" s="3">
         <v>325100</v>
@@ -1973,11 +1973,11 @@
       <c r="E57" s="3">
         <v>298700</v>
       </c>
-      <c r="F57" s="3">
-        <v>298200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>298200</v>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H57" s="3">
         <v>291100</v>
@@ -1985,8 +1985,8 @@
       <c r="I57" s="3">
         <v>291100</v>
       </c>
-      <c r="J57" s="3">
-        <v>282700</v>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>282700</v>
@@ -2002,11 +2002,11 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2014,8 +2014,8 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2060,11 +2060,11 @@
       <c r="E60" s="3">
         <v>299900</v>
       </c>
-      <c r="F60" s="3">
-        <v>298200</v>
-      </c>
-      <c r="G60" s="3">
-        <v>298200</v>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H60" s="3">
         <v>291200</v>
@@ -2072,8 +2072,8 @@
       <c r="I60" s="3">
         <v>291200</v>
       </c>
-      <c r="J60" s="3">
-        <v>282700</v>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>282700</v>
@@ -2090,10 +2090,10 @@
         <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>400</v>
@@ -2102,7 +2102,7 @@
         <v>400</v>
       </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>400</v>
@@ -2118,11 +2118,11 @@
       <c r="E62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3900</v>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3">
         <v>1100</v>
@@ -2130,8 +2130,8 @@
       <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
-        <v>4300</v>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>4300</v>
@@ -2234,11 +2234,11 @@
       <c r="E66" s="3">
         <v>302100</v>
       </c>
-      <c r="F66" s="3">
-        <v>302500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>302500</v>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H66" s="3">
         <v>293600</v>
@@ -2246,8 +2246,8 @@
       <c r="I66" s="3">
         <v>293600</v>
       </c>
-      <c r="J66" s="3">
-        <v>287400</v>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K66" s="3">
         <v>287400</v>
@@ -2392,11 +2392,11 @@
       <c r="E72" s="3">
         <v>29400</v>
       </c>
-      <c r="F72" s="3">
-        <v>29200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>29200</v>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3">
         <v>29100</v>
@@ -2404,8 +2404,8 @@
       <c r="I72" s="3">
         <v>29100</v>
       </c>
-      <c r="J72" s="3">
-        <v>29000</v>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K72" s="3">
         <v>29000</v>
@@ -2508,11 +2508,11 @@
       <c r="E76" s="3">
         <v>37100</v>
       </c>
-      <c r="F76" s="3">
-        <v>37200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>37200</v>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H76" s="3">
         <v>37300</v>
@@ -2520,8 +2520,8 @@
       <c r="I76" s="3">
         <v>37300</v>
       </c>
-      <c r="J76" s="3">
-        <v>37700</v>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K76" s="3">
         <v>37700</v>
@@ -2600,11 +2600,11 @@
       <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
-        <v>500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>500</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H81" s="3">
         <v>600</v>
@@ -2612,8 +2612,8 @@
       <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
-        <v>600</v>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3">
         <v>600</v>
